--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_154_R16.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_154_R16.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4786</v>
+        <v>7.3427</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8252</v>
+        <v>5.0925</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6535</v>
+        <v>2.2502</v>
       </c>
       <c r="G2" t="n">
         <v>3.9468</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3875</v>
+        <v>0.2515</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2197</v>
+        <v>0.0477</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6071</v>
+        <v>0.2038</v>
       </c>
       <c r="V2" t="n">
         <v>2.6805</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7503</v>
+        <v>4.4125</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6183</v>
+        <v>3.4623</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.868</v>
+        <v>0.9502</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7051</v>
+        <v>2.7457</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6515</v>
+        <v>-0.4261</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0536</v>
+        <v>3.1719</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5336</v>
+        <v>3.5182</v>
       </c>
       <c r="K3" t="n">
-        <v>4.4232</v>
+        <v>0.3431</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1104</v>
+        <v>3.1752</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1715</v>
+        <v>-0.7725</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2283</v>
+        <v>-0.7692</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0568</v>
+        <v>-0.0033</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>2.906</v>
+        <v>-0.1013</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9609</v>
+        <v>0.2636</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0549</v>
+        <v>-0.3648</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.8608</v>
+        <v>1.0722</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9607</v>
+        <v>3.8026</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3129</v>
+        <v>4.5698</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6478</v>
+        <v>-0.7672</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7457</v>
+        <v>4.7051</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4261</v>
+        <v>4.6515</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1719</v>
+        <v>0.0536</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5182</v>
+        <v>4.5336</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3431</v>
+        <v>4.4232</v>
       </c>
       <c r="L4" t="n">
-        <v>3.1752</v>
+        <v>0.1104</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7725</v>
+        <v>0.1715</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7692</v>
+        <v>0.2283</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0033</v>
+        <v>-0.0568</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5531</v>
+        <v>0.9583</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1142</v>
+        <v>0.9124</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6673</v>
+        <v>0.0459</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0722</v>
+        <v>-1.8608</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0.2836</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3965</v>
+        <v>2.1331</v>
       </c>
       <c r="E5" t="n">
-        <v>3.3869</v>
+        <v>2.7538</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9903999999999999</v>
+        <v>-0.6207</v>
       </c>
       <c r="G5" t="n">
         <v>2.1982</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1287</v>
+        <v>-0.1346</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7512</v>
+        <v>0.1182</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.2528</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3943</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8248</v>
+        <v>1.1765</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.701</v>
+        <v>-0.3157</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5258</v>
+        <v>1.4922</v>
       </c>
       <c r="G6" t="n">
         <v>1.0795</v>
@@ -922,13 +922,13 @@
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1129</v>
+        <v>0.2388</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.224</v>
+        <v>0.1612</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1111</v>
+        <v>0.0775</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1418</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2872</v>
+        <v>-0.5899</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.5161</v>
+        <v>-3.777</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2289</v>
+        <v>3.1871</v>
       </c>
       <c r="G7" t="n">
         <v>-2.9771</v>
@@ -1000,13 +1000,13 @@
         <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>1.762</v>
+        <v>1.4594</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4832</v>
+        <v>0.2559</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2453</v>
+        <v>1.2035</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9121</v>
+        <v>-1.2387</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1594</v>
+        <v>-1.6876</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2473</v>
+        <v>0.449</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7295</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4145</v>
+        <v>-0.7411</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8215</v>
+        <v>-0.3497</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.593</v>
+        <v>-0.3914</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3257</v>
+        <v>-2.0803</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.897</v>
+        <v>-1.1893</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4287</v>
+        <v>-0.891</v>
       </c>
       <c r="G9" t="n">
         <v>-0.6459</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.2519</v>
+        <v>-1.0064</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2696</v>
+        <v>-0.5619</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9823</v>
+        <v>-0.4446</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3558</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.891</v>
+        <v>-6.2169</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.147</v>
+        <v>-6.4393</v>
       </c>
       <c r="F10" t="n">
-        <v>0.256</v>
+        <v>0.2224</v>
       </c>
       <c r="G10" t="n">
         <v>-2.1235</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8913</v>
+        <v>-0.2172</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1202</v>
+        <v>-0.4125</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2289</v>
+        <v>0.1953</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3247</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.994900000000003</v>
+        <v>8.741599999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>1.722800000000001</v>
+        <v>2.469499999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>6.272200000000002</v>
+        <v>6.2722</v>
       </c>
       <c r="G11" t="n">
-        <v>8.199299999999999</v>
+        <v>8.199300000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9298</v>
+        <v>2.929800000000001</v>
       </c>
       <c r="I11" t="n">
         <v>5.269500000000001</v>
@@ -1288,7 +1288,7 @@
         <v>10.4179</v>
       </c>
       <c r="K11" t="n">
-        <v>5.634499999999998</v>
+        <v>5.634499999999999</v>
       </c>
       <c r="L11" t="n">
         <v>4.7834</v>
@@ -1312,10 +1312,10 @@
         <v>15.0771</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.03950000000000009</v>
+        <v>0.7074</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3119000000000001</v>
+        <v>0.4349</v>
       </c>
       <c r="U11" t="n">
         <v>0.2723999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.2241</v>
+        <v>5.9997</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0854</v>
+        <v>7.029</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8613</v>
+        <v>-1.0294</v>
       </c>
       <c r="G12" t="n">
         <v>5.2956</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3756</v>
+        <v>0.4</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8883</v>
+        <v>0.0553</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5127</v>
+        <v>0.3446</v>
       </c>
       <c r="V12" t="n">
         <v>0.5361</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2632</v>
+        <v>2.4217</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0049</v>
+        <v>2.5331</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2583</v>
+        <v>-0.1114</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7478</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9905</v>
+        <v>1.149</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9831</v>
+        <v>0.5113</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0073</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>1.3247</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1209</v>
+        <v>2.2046</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.6407</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3623</v>
+        <v>1.5639</v>
       </c>
       <c r="G14" t="n">
         <v>1.7466</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3216</v>
+        <v>-0.2379</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0395</v>
+        <v>-0.0784</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3611</v>
+        <v>-0.1595</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.03</v>
+        <v>0.6768</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4284</v>
+        <v>0.3105</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6016</v>
+        <v>0.3664</v>
       </c>
       <c r="G15" t="n">
         <v>-0.8691</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2754</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0395</v>
+        <v>-0.0784</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2359</v>
+        <v>0.0007</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.5797</v>
+        <v>-1.7319</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3379</v>
+        <v>-3.3963</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2418</v>
+        <v>1.6644</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.6563</v>
+        <v>0.3538</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2908</v>
+        <v>-2.1523</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.3654</v>
+        <v>2.5061</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.0618</v>
+        <v>0.508</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3859</v>
+        <v>-0.9005</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6758999999999999</v>
+        <v>1.4085</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5944</v>
+        <v>-0.1542</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9049</v>
+        <v>-1.2518</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6895</v>
+        <v>1.0976</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3807</v>
+        <v>-0.6065</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8837</v>
+        <v>-0.4793</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.503</v>
+        <v>-0.1272</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0027</v>
+        <v>-2.4403</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.104</v>
+        <v>-1.6353</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1013</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3538</v>
+        <v>-3.6563</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.1523</v>
+        <v>-1.2908</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5061</v>
+        <v>-2.3654</v>
       </c>
       <c r="J17" t="n">
-        <v>0.508</v>
+        <v>-1.0618</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9005</v>
+        <v>-0.3859</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4085</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1542</v>
+        <v>-2.5944</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2518</v>
+        <v>-0.9049</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0976</v>
+        <v>-1.6895</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8773</v>
+        <v>0.5201</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.187</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3097</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.231</v>
+        <v>-3.4054</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.8253</v>
+        <v>-2.9997</v>
       </c>
       <c r="F18" t="n">
         <v>-0.4057</v>
@@ -1858,10 +1858,10 @@
         <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7141</v>
+        <v>-0.8885</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.411</v>
+        <v>-0.5854</v>
       </c>
       <c r="U18" t="n">
         <v>-0.3031</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.9725</v>
+        <v>-4.8045</v>
       </c>
       <c r="E19" t="n">
         <v>-3.2165</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.756</v>
+        <v>-1.588</v>
       </c>
       <c r="G19" t="n">
         <v>-3.7215</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2851</v>
+        <v>0.4531</v>
       </c>
       <c r="T19" t="n">
         <v>0.1142</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1709</v>
+        <v>0.3389</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.8471</v>
+        <v>-6.9156</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.0658</v>
+        <v>-5.5376</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7813</v>
+        <v>-1.378</v>
       </c>
       <c r="G20" t="n">
         <v>-4.8518</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6036</v>
+        <v>-0.6721</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1537</v>
+        <v>-0.3181</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7573</v>
+        <v>-0.3541</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.994800000000001</v>
+        <v>-7.9949</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.272200000000002</v>
+        <v>-6.272099999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7226</v>
+        <v>-1.7227</v>
       </c>
       <c r="G21" t="n">
         <v>-8.199300000000001</v>
@@ -2092,13 +2092,13 @@
         <v>13.9173</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0395000000000002</v>
+        <v>0.03939999999999977</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2726000000000001</v>
+        <v>-0.2726</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3120000000000002</v>
+        <v>0.3117999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>1.3247</v>
